--- a/Assets/Data/GameDB.xlsx
+++ b/Assets/Data/GameDB.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Player" sheetId="1" r:id="rId1"/>
     <sheet name="Weapon" sheetId="2" r:id="rId2"/>
     <sheet name="AI" sheetId="3" r:id="rId3"/>
+    <sheet name="Monster" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="84">
   <si>
     <t xml:space="preserve">name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -254,6 +255,73 @@
   <si>
     <t xml:space="preserve">Respawn</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groggy_Max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase2_Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part1_HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part2_HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reward_Val</t>
+  </si>
+  <si>
+    <t xml:space="preserve">늙은 사냥개</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">굶주린 늑대</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">우두머리 늑대</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부패한 키메라</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">단두대</t>
+  </si>
+  <si>
+    <t xml:space="preserve">관 뚜껑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SwordShield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">묘비의 쐐기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spear</t>
   </si>
 </sst>
 </file>
@@ -845,7 +913,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>28</v>
@@ -857,10 +925,10 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H2">
         <v>30</v>
@@ -869,19 +937,19 @@
         <v>6</v>
       </c>
       <c r="J2">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K2">
         <v>10</v>
       </c>
       <c r="L2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M2">
         <v>12</v>
       </c>
       <c r="N2">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="O2">
         <v>15</v>
@@ -898,46 +966,46 @@
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3">
+        <v>12</v>
+      </c>
+      <c r="H3">
+        <v>20</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>15</v>
+      </c>
+      <c r="K3">
+        <v>8</v>
+      </c>
+      <c r="L3">
         <v>25</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3">
-        <v>0.6</v>
-      </c>
-      <c r="E3">
-        <v>15</v>
-      </c>
-      <c r="F3">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>25</v>
-      </c>
-      <c r="H3">
-        <v>40</v>
-      </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
-      <c r="J3">
-        <v>35</v>
-      </c>
-      <c r="K3">
+      <c r="M3">
+        <v>10</v>
+      </c>
+      <c r="N3">
+        <v>100</v>
+      </c>
+      <c r="O3">
         <v>12</v>
-      </c>
-      <c r="L3">
-        <v>50</v>
-      </c>
-      <c r="M3">
-        <v>15</v>
-      </c>
-      <c r="N3">
-        <v>0.5</v>
-      </c>
-      <c r="O3">
-        <v>20</v>
       </c>
       <c r="P3">
         <v>200</v>
@@ -951,13 +1019,13 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D4">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -975,22 +1043,22 @@
         <v>4</v>
       </c>
       <c r="J4">
+        <v>15</v>
+      </c>
+      <c r="K4">
+        <v>6</v>
+      </c>
+      <c r="L4">
         <v>20</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>8</v>
       </c>
-      <c r="L4">
-        <v>25</v>
-      </c>
-      <c r="M4">
-        <v>25</v>
-      </c>
       <c r="N4">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P4">
         <v>120</v>
@@ -1004,52 +1072,52 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H5">
+        <v>25</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>30</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
         <v>20</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>25</v>
-      </c>
-      <c r="K5">
-        <v>10</v>
-      </c>
-      <c r="L5">
-        <v>10</v>
       </c>
       <c r="M5">
         <v>10</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="Q5">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1260,4 +1328,198 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="14.08203125" customWidth="1"/>
+    <col min="3" max="3" width="13.08203125" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="11" max="11" width="14.4140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="4">
+        <v>500</v>
+      </c>
+      <c r="F2" s="4">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4">
+        <v>100</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="4">
+        <v>40</v>
+      </c>
+      <c r="F3" s="4">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4">
+        <v>20</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="4">
+        <v>800</v>
+      </c>
+      <c r="F4" s="4">
+        <v>20</v>
+      </c>
+      <c r="G4" s="4">
+        <v>200</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2500</v>
+      </c>
+      <c r="F5" s="4">
+        <v>25</v>
+      </c>
+      <c r="G5" s="4">
+        <v>500</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I5" s="4">
+        <v>300</v>
+      </c>
+      <c r="J5" s="4">
+        <v>200</v>
+      </c>
+      <c r="K5" s="4">
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/Data/GameDB.xlsx
+++ b/Assets/Data/GameDB.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="84">
   <si>
     <t xml:space="preserve">name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -919,7 +919,7 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E2">
         <v>10</v>

--- a/Assets/Data/GameDB.xlsx
+++ b/Assets/Data/GameDB.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="85">
   <si>
     <t xml:space="preserve">name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t xml:space="preserve">Spear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">플레이어</t>
   </si>
 </sst>
 </file>
@@ -810,7 +813,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -819,7 +822,7 @@
         <v>5</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>0.4</v>
@@ -831,10 +834,10 @@
         <v>100</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/GameDB.xlsx
+++ b/Assets/Data/GameDB.xlsx
@@ -1,24 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Fork\Last-Rites\Assets\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15EA7754-48B6-41AC-8842-C411ED8239CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Player" sheetId="1" r:id="rId1"/>
     <sheet name="Weapon" sheetId="2" r:id="rId2"/>
     <sheet name="AI" sheetId="3" r:id="rId3"/>
     <sheet name="Monster" sheetId="4" r:id="rId4"/>
+    <sheet name="Item_Data" sheetId="5" r:id="rId5"/>
+    <sheet name="Shop_Recipe" sheetId="6" r:id="rId6"/>
+    <sheet name="Shop_Potion" sheetId="7" r:id="rId7"/>
+    <sheet name="Shop_AI_Unlock" sheetId="8" r:id="rId8"/>
+    <sheet name="Blacksmith_Enhance" sheetId="9" r:id="rId9"/>
+    <sheet name="Blacksmith_Infusion" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" chartTrackingRefBase="1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -33,305 +45,546 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="85">
-  <si>
-    <t xml:space="preserve">name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">HP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Dash_Time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Move_Spd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Dash_Spd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Dash_Cool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Max_Stamina</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Stamina_Regen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Dash_Cost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">장의사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Atk_Spd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Combo_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combo_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Combo_3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_Dmg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Q_Cool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">W_Dmg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">W_Cool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">E_Dmg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">E_Cool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">R_Cool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">V_Dmg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">V_Cool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">철의 처녀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">망자 향로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">사슬 낫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">영혼 랜턴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GreatSword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DualBlade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R_Val</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">PlayerID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">WeaponID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Atk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1_Val</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1_Cool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2_Val</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2_Cool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">수호기사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도발</t>
-  </si>
-  <si>
-    <t xml:space="preserve">방패치기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">물의 사제</t>
-  </si>
-  <si>
-    <t xml:space="preserve">치유</t>
-  </si>
-  <si>
-    <t xml:space="preserve">축복</t>
-  </si>
-  <si>
-    <t xml:space="preserve">광전사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">휠윈드</t>
-  </si>
-  <si>
-    <t xml:space="preserve">격분</t>
-  </si>
-  <si>
-    <t xml:space="preserve">그림자 사수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격</t>
-  </si>
-  <si>
-    <t xml:space="preserve">덫</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AiID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Tanker</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Healer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Dealer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranger</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Respawn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Groggy_Max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase2_Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part1_HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part2_HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reward_Val</t>
-  </si>
-  <si>
-    <t xml:space="preserve">늙은 사냥개</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">굶주린 늑대</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">우두머리 늑대</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부패한 키메라</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">단두대</t>
-  </si>
-  <si>
-    <t xml:space="preserve">관 뚜껑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SwordShield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">묘비의 쐐기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">플레이어</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="166">
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dash_Time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Move_Spd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dash_Spd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dash_Cool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max_Stamina</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina_Regen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dash_Cost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atk_Spd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Combo_1</t>
+  </si>
+  <si>
+    <t>Combo_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Combo_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q_Dmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q_Cool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>W_Dmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>W_Cool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_Dmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E_Cool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R_Cool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V_Dmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V_Cool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreatSword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DualBlade</t>
+  </si>
+  <si>
+    <t>R_Val</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atk</t>
+  </si>
+  <si>
+    <t>S1_Name</t>
+  </si>
+  <si>
+    <t>S1_Val</t>
+  </si>
+  <si>
+    <t>S1_Cool</t>
+  </si>
+  <si>
+    <t>S2_Name</t>
+  </si>
+  <si>
+    <t>S2_Val</t>
+  </si>
+  <si>
+    <t>S2_Cool</t>
+  </si>
+  <si>
+    <t>수호기사</t>
+  </si>
+  <si>
+    <t>도발</t>
+  </si>
+  <si>
+    <t>방패치기</t>
+  </si>
+  <si>
+    <t>물의 사제</t>
+  </si>
+  <si>
+    <t>치유</t>
+  </si>
+  <si>
+    <t>축복</t>
+  </si>
+  <si>
+    <t>광전사</t>
+  </si>
+  <si>
+    <t>휠윈드</t>
+  </si>
+  <si>
+    <t>격분</t>
+  </si>
+  <si>
+    <t>그림자 사수</t>
+  </si>
+  <si>
+    <t>저격</t>
+  </si>
+  <si>
+    <t>덫</t>
+  </si>
+  <si>
+    <t>AiID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Role</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tanker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Healer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dealer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Respawn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>Groggy_Max</t>
+  </si>
+  <si>
+    <t>Phase2_Rate</t>
+  </si>
+  <si>
+    <t>Part1_HP</t>
+  </si>
+  <si>
+    <t>Part2_HP</t>
+  </si>
+  <si>
+    <t>Reward_Val</t>
+  </si>
+  <si>
+    <t>늙은 사냥개</t>
+  </si>
+  <si>
+    <t>Beast</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>굶주린 늑대</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>우두머리 늑대</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>부패한 키메라</t>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단두대</t>
+  </si>
+  <si>
+    <t>관 뚜껑</t>
+  </si>
+  <si>
+    <t>SwordShield</t>
+  </si>
+  <si>
+    <t>가위</t>
+  </si>
+  <si>
+    <t>묘비의 쐐기</t>
+  </si>
+  <si>
+    <t>Spear</t>
+  </si>
+  <si>
+    <t>플레이어</t>
+  </si>
+  <si>
+    <t>ItemId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>C_001</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>R_001</t>
+  </si>
+  <si>
+    <t>Raw</t>
+  </si>
+  <si>
+    <t>R_002</t>
+  </si>
+  <si>
+    <t>R_003</t>
+  </si>
+  <si>
+    <t>P_001</t>
+  </si>
+  <si>
+    <t>Processed</t>
+  </si>
+  <si>
+    <t>P_002</t>
+  </si>
+  <si>
+    <t>P_003</t>
+  </si>
+  <si>
+    <t>S_000</t>
+  </si>
+  <si>
+    <t>BossSoul</t>
+  </si>
+  <si>
+    <t>S_001</t>
+  </si>
+  <si>
+    <t>S_002</t>
+  </si>
+  <si>
+    <t>S_003</t>
+  </si>
+  <si>
+    <t>Max_Stack</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>망자의 유물</t>
+  </si>
+  <si>
+    <t>오염된 야수의 뼈</t>
+  </si>
+  <si>
+    <t>1구역 짐승들에게서 얻은 탁하고 붉은 뼛조각.</t>
+  </si>
+  <si>
+    <t>일그러진 강철 파편</t>
+  </si>
+  <si>
+    <t>2구역 언데드 기사형 몬스터 드랍 전리품.</t>
+  </si>
+  <si>
+    <t>심연의 진흙</t>
+  </si>
+  <si>
+    <t>상위 구역 몬스터 드랍 전리품.</t>
+  </si>
+  <si>
+    <t>정화된 뼛가루</t>
+  </si>
+  <si>
+    <t>항아리에서 정화한 하얀 가루. (1~3강 재료)</t>
+  </si>
+  <si>
+    <t>진혼의 쐐기석</t>
+  </si>
+  <si>
+    <t>강철과 유물을 벼려낸 결정. (4~6강 재료)</t>
+  </si>
+  <si>
+    <t>망각의 결정</t>
+  </si>
+  <si>
+    <t>최종 무기 강화 재료. (7~10강 재료)</t>
+  </si>
+  <si>
+    <t>늑대 왕의 영혼</t>
+  </si>
+  <si>
+    <t>튜토리얼 0F 보스 처치 보상 (대지 속성)</t>
+  </si>
+  <si>
+    <t>(테마 1 보스)의 영혼</t>
+  </si>
+  <si>
+    <t>테마 1 메인 보스 처치 보상 (화염 속성)</t>
+  </si>
+  <si>
+    <t>(테마 2 보스)의 영혼</t>
+  </si>
+  <si>
+    <t>테마 2 메인 보스 처치 보상 (서리 속성)</t>
+  </si>
+  <si>
+    <t>(테마 3 보스)의 영혼</t>
+  </si>
+  <si>
+    <t>테마 3 메인 보스 처치 보상 (부패 속성)</t>
+  </si>
+  <si>
+    <t>Result_Id</t>
+  </si>
+  <si>
+    <t>Result_Amt</t>
+  </si>
+  <si>
+    <t>Mat_Id</t>
+  </si>
+  <si>
+    <t>Mat_Amt</t>
+  </si>
+  <si>
+    <t>Cost_Id</t>
+  </si>
+  <si>
+    <t>Cost_Amt</t>
+  </si>
+  <si>
+    <t>Potion_Lv</t>
+  </si>
+  <si>
+    <t>Max_Count</t>
+  </si>
+  <si>
+    <t>Heal_Percent</t>
+  </si>
+  <si>
+    <t>Req_Mat_Id_1</t>
+  </si>
+  <si>
+    <t>Req_Mat_Amt_1</t>
+  </si>
+  <si>
+    <t>Req_Mat_Id_2</t>
+  </si>
+  <si>
+    <t>Req_Mat_Amt_2</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>AI_Id</t>
+  </si>
+  <si>
+    <t>Unlock_Condition</t>
+  </si>
+  <si>
+    <t>AI_001</t>
+  </si>
+  <si>
+    <t>충견의 영혼</t>
+  </si>
+  <si>
+    <t>Clear_0F (자동)</t>
+  </si>
+  <si>
+    <t>AI_002</t>
+  </si>
+  <si>
+    <t>성기사의 영혼</t>
+  </si>
+  <si>
+    <t>AI_003</t>
+  </si>
+  <si>
+    <t>광전사의 영혼</t>
+  </si>
+  <si>
+    <t>Clear_1F</t>
+  </si>
+  <si>
+    <t>AI_004</t>
+  </si>
+  <si>
+    <t>궁수의 영혼</t>
+  </si>
+  <si>
+    <t>Clear_2F</t>
+  </si>
+  <si>
+    <t>Enhance_Lv</t>
+  </si>
+  <si>
+    <t>Success_Rate</t>
+  </si>
+  <si>
+    <t>Fail_Bonus</t>
+  </si>
+  <si>
+    <t>Req_Mat_Id</t>
+  </si>
+  <si>
+    <t>Req_Mat_Amt</t>
+  </si>
+  <si>
+    <t>Req_Cost_Id</t>
+  </si>
+  <si>
+    <t>Req_Cost_Amt</t>
+  </si>
+  <si>
+    <t>Soul_Id</t>
+  </si>
+  <si>
+    <t>Target_Weapon</t>
+  </si>
+  <si>
+    <t>Effect_Value</t>
+  </si>
+  <si>
+    <t>Effect_Desc</t>
+  </si>
+  <si>
+    <t>대지 (Earth)</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>강인도(Poise) 깎는 수치 20% 증가</t>
+  </si>
+  <si>
+    <t>화염 (Fire)</t>
+  </si>
+  <si>
+    <t>5초간 최대 체력 비례 화상 도트 데미지</t>
+  </si>
+  <si>
+    <t>서리 (Frost)</t>
+  </si>
+  <si>
+    <t>적의 이동 및 공격 모션 속도 15% 둔화</t>
+  </si>
+  <si>
+    <t>부패 (Decay)</t>
+  </si>
+  <si>
+    <t>적 방어력 감소, 이후 받는 피해량 15% 증가</t>
+  </si>
+  <si>
+    <t>이승을 떠나지 못한 망자들의 미련이 뭉친 조각.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -379,7 +632,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -402,13 +655,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -430,6 +729,60 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -437,11 +790,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -735,7 +1088,7 @@
   <a:objectDefaults>
     <a:lnDef>
       <a:spPr/>
-      <a:bodyPr rtlCol="0"/>
+      <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
         <a:lnRef idx="2">
@@ -763,7 +1116,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
@@ -778,7 +1131,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -813,7 +1166,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -846,8 +1199,133 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.75" customWidth="1"/>
+    <col min="2" max="2" width="13.4140625" customWidth="1"/>
+    <col min="3" max="3" width="14.4140625" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+    </row>
+    <row r="3" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" s="8">
+        <v>5</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+    </row>
+    <row r="4" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+    </row>
+    <row r="5" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E4:H4"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
@@ -860,55 +1338,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.45">
@@ -916,10 +1394,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>0.6</v>
@@ -969,10 +1447,10 @@
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1022,10 +1500,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D4">
         <v>1.6</v>
@@ -1075,10 +1553,10 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D5">
         <v>1.2</v>
@@ -1130,7 +1608,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1139,40 +1617,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1180,10 +1658,10 @@
         <v>100</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D2" s="4">
         <v>300</v>
@@ -1195,7 +1673,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H2" s="4">
         <v>5</v>
@@ -1204,7 +1682,7 @@
         <v>12</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K2" s="4">
         <v>2</v>
@@ -1218,10 +1696,10 @@
         <v>101</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D3" s="4">
         <v>150</v>
@@ -1233,7 +1711,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H3" s="4">
         <v>30</v>
@@ -1242,7 +1720,7 @@
         <v>15</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="K3" s="4">
         <v>20</v>
@@ -1256,10 +1734,10 @@
         <v>102</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D4" s="4">
         <v>200</v>
@@ -1271,7 +1749,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H4" s="4">
         <v>12</v>
@@ -1280,7 +1758,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K4" s="4">
         <v>1.5</v>
@@ -1294,10 +1772,10 @@
         <v>103</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4">
         <v>120</v>
@@ -1309,7 +1787,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H5" s="4">
         <v>40</v>
@@ -1318,7 +1796,7 @@
         <v>8</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="K5" s="4">
         <v>3</v>
@@ -1334,7 +1812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1348,177 +1826,1069 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="22">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="23">
+        <v>500</v>
+      </c>
+      <c r="F2" s="23">
         <v>10</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="G2" s="23">
+        <v>100</v>
+      </c>
+      <c r="H2" s="23">
+        <v>0.6</v>
+      </c>
+      <c r="I2" s="23">
+        <v>0</v>
+      </c>
+      <c r="J2" s="23">
+        <v>0</v>
+      </c>
+      <c r="K2" s="23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="22">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="D3" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="23">
+        <v>40</v>
+      </c>
+      <c r="F3" s="23">
+        <v>5</v>
+      </c>
+      <c r="G3" s="23">
+        <v>20</v>
+      </c>
+      <c r="H3" s="23">
+        <v>0</v>
+      </c>
+      <c r="I3" s="23">
+        <v>0</v>
+      </c>
+      <c r="J3" s="23">
+        <v>0</v>
+      </c>
+      <c r="K3" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="23">
+        <v>800</v>
+      </c>
+      <c r="F4" s="23">
+        <v>20</v>
+      </c>
+      <c r="G4" s="23">
+        <v>200</v>
+      </c>
+      <c r="H4" s="23">
+        <v>0</v>
+      </c>
+      <c r="I4" s="23">
+        <v>0</v>
+      </c>
+      <c r="J4" s="23">
+        <v>0</v>
+      </c>
+      <c r="K4" s="23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="23">
+        <v>2500</v>
+      </c>
+      <c r="F5" s="23">
+        <v>25</v>
+      </c>
+      <c r="G5" s="23">
+        <v>500</v>
+      </c>
+      <c r="H5" s="23">
+        <v>0.6</v>
+      </c>
+      <c r="I5" s="23">
+        <v>300</v>
+      </c>
+      <c r="J5" s="23">
+        <v>200</v>
+      </c>
+      <c r="K5" s="23">
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="7.9140625" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="23.4140625" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="33.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="20"/>
+    </row>
+    <row r="2" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="4">
+        <v>9999</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="4">
+        <v>999</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="4">
+        <v>999</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="4">
+        <v>999</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="4">
+        <v>999</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="4">
+        <v>999</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="4">
+        <v>999</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E1:H1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="10.4140625" customWidth="1"/>
+    <col min="2" max="2" width="10.58203125" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="4">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="4">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="4">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="4">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.4140625" customWidth="1"/>
+    <col min="5" max="5" width="17.08203125" customWidth="1"/>
+    <col min="6" max="6" width="15.58203125" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8">
+        <v>3</v>
+      </c>
+      <c r="C2" s="8">
+        <v>30</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="7">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8">
+        <v>4</v>
+      </c>
+      <c r="C3" s="8">
         <v>35</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>71</v>
+      <c r="D3" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="7">
+        <v>500</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8">
+        <v>5</v>
+      </c>
+      <c r="C4" s="8">
+        <v>40</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1500</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="13.58203125" customWidth="1"/>
+    <col min="2" max="2" width="15.08203125" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1"/>
+    <col min="5" max="5" width="17.4140625" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.4140625" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.9140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
+        <v>100</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="E2" s="4">
-        <v>500</v>
-      </c>
-      <c r="F2" s="4">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="G2" s="4">
         <v>100</v>
       </c>
-      <c r="H2" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I2" s="4">
+    </row>
+    <row r="3" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4">
+        <v>100</v>
+      </c>
+      <c r="C3" s="4">
         <v>0</v>
       </c>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>73</v>
+      <c r="D3" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="E3" s="4">
-        <v>40</v>
-      </c>
-      <c r="F3" s="4">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="G3" s="4">
-        <v>20</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4">
+        <v>80</v>
+      </c>
+      <c r="C4" s="4">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>75</v>
+      <c r="D4" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="E4" s="4">
-        <v>800</v>
-      </c>
-      <c r="F4" s="4">
-        <v>20</v>
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="G4" s="4">
         <v>200</v>
       </c>
-      <c r="H4" s="4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>71</v>
+    </row>
+    <row r="5" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>60</v>
+      </c>
+      <c r="C5" s="4">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="E5" s="4">
-        <v>2500</v>
-      </c>
-      <c r="F5" s="4">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>40</v>
+      </c>
+      <c r="C6" s="4">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
         <v>25</v>
       </c>
-      <c r="G5" s="4">
-        <v>500</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I5" s="4">
-        <v>300</v>
-      </c>
-      <c r="J5" s="4">
-        <v>200</v>
-      </c>
-      <c r="K5" s="4">
-        <v>500</v>
+      <c r="C7" s="4">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="4">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4">
+        <v>15</v>
+      </c>
+      <c r="C8" s="4">
+        <v>5</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="4">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4">
+        <v>3</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="4">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="4">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="4">
+        <v>5</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="4">
+        <v>3000</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/GameDB.xlsx
+++ b/Assets/Data/GameDB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Fork\Last-Rites\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15EA7754-48B6-41AC-8842-C411ED8239CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD98A612-5C67-46BD-AC7D-3AC574B049C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Player" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="168">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -320,265 +320,276 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>C_001</t>
   </si>
   <si>
+    <t>R_001</t>
+  </si>
+  <si>
+    <t>Raw</t>
+  </si>
+  <si>
+    <t>R_002</t>
+  </si>
+  <si>
+    <t>R_003</t>
+  </si>
+  <si>
+    <t>P_001</t>
+  </si>
+  <si>
+    <t>Processed</t>
+  </si>
+  <si>
+    <t>P_002</t>
+  </si>
+  <si>
+    <t>P_003</t>
+  </si>
+  <si>
+    <t>S_000</t>
+  </si>
+  <si>
+    <t>BossSoul</t>
+  </si>
+  <si>
+    <t>S_001</t>
+  </si>
+  <si>
+    <t>S_002</t>
+  </si>
+  <si>
+    <t>S_003</t>
+  </si>
+  <si>
+    <t>Max_Stack</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>망자의 유물</t>
+  </si>
+  <si>
+    <t>오염된 야수의 뼈</t>
+  </si>
+  <si>
+    <t>1구역 짐승들에게서 얻은 탁하고 붉은 뼛조각.</t>
+  </si>
+  <si>
+    <t>일그러진 강철 파편</t>
+  </si>
+  <si>
+    <t>2구역 언데드 기사형 몬스터 드랍 전리품.</t>
+  </si>
+  <si>
+    <t>심연의 진흙</t>
+  </si>
+  <si>
+    <t>상위 구역 몬스터 드랍 전리품.</t>
+  </si>
+  <si>
+    <t>정화된 뼛가루</t>
+  </si>
+  <si>
+    <t>항아리에서 정화한 하얀 가루. (1~3강 재료)</t>
+  </si>
+  <si>
+    <t>진혼의 쐐기석</t>
+  </si>
+  <si>
+    <t>강철과 유물을 벼려낸 결정. (4~6강 재료)</t>
+  </si>
+  <si>
+    <t>망각의 결정</t>
+  </si>
+  <si>
+    <t>최종 무기 강화 재료. (7~10강 재료)</t>
+  </si>
+  <si>
+    <t>늑대 왕의 영혼</t>
+  </si>
+  <si>
+    <t>튜토리얼 0F 보스 처치 보상 (대지 속성)</t>
+  </si>
+  <si>
+    <t>(테마 1 보스)의 영혼</t>
+  </si>
+  <si>
+    <t>테마 1 메인 보스 처치 보상 (화염 속성)</t>
+  </si>
+  <si>
+    <t>(테마 2 보스)의 영혼</t>
+  </si>
+  <si>
+    <t>테마 2 메인 보스 처치 보상 (서리 속성)</t>
+  </si>
+  <si>
+    <t>(테마 3 보스)의 영혼</t>
+  </si>
+  <si>
+    <t>테마 3 메인 보스 처치 보상 (부패 속성)</t>
+  </si>
+  <si>
+    <t>Result_Id</t>
+  </si>
+  <si>
+    <t>Result_Amt</t>
+  </si>
+  <si>
+    <t>Mat_Id</t>
+  </si>
+  <si>
+    <t>Mat_Amt</t>
+  </si>
+  <si>
+    <t>Cost_Id</t>
+  </si>
+  <si>
+    <t>Cost_Amt</t>
+  </si>
+  <si>
+    <t>Potion_Lv</t>
+  </si>
+  <si>
+    <t>Max_Count</t>
+  </si>
+  <si>
+    <t>Heal_Percent</t>
+  </si>
+  <si>
+    <t>Req_Mat_Id_1</t>
+  </si>
+  <si>
+    <t>Req_Mat_Amt_1</t>
+  </si>
+  <si>
+    <t>Req_Mat_Id_2</t>
+  </si>
+  <si>
+    <t>Req_Mat_Amt_2</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>AI_Id</t>
+  </si>
+  <si>
+    <t>AI_001</t>
+  </si>
+  <si>
+    <t>충견의 영혼</t>
+  </si>
+  <si>
+    <t>Clear_0F (자동)</t>
+  </si>
+  <si>
+    <t>AI_002</t>
+  </si>
+  <si>
+    <t>성기사의 영혼</t>
+  </si>
+  <si>
+    <t>AI_003</t>
+  </si>
+  <si>
+    <t>광전사의 영혼</t>
+  </si>
+  <si>
+    <t>Clear_1F</t>
+  </si>
+  <si>
+    <t>AI_004</t>
+  </si>
+  <si>
+    <t>궁수의 영혼</t>
+  </si>
+  <si>
+    <t>Clear_2F</t>
+  </si>
+  <si>
+    <t>Enhance_Lv</t>
+  </si>
+  <si>
+    <t>Success_Rate</t>
+  </si>
+  <si>
+    <t>Fail_Bonus</t>
+  </si>
+  <si>
+    <t>Req_Mat_Id</t>
+  </si>
+  <si>
+    <t>Req_Mat_Amt</t>
+  </si>
+  <si>
+    <t>Req_Cost_Id</t>
+  </si>
+  <si>
+    <t>Req_Cost_Amt</t>
+  </si>
+  <si>
+    <t>Soul_Id</t>
+  </si>
+  <si>
+    <t>Target_Weapon</t>
+  </si>
+  <si>
+    <t>Effect_Value</t>
+  </si>
+  <si>
+    <t>Effect_Desc</t>
+  </si>
+  <si>
+    <t>대지 (Earth)</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>강인도(Poise) 깎는 수치 20% 증가</t>
+  </si>
+  <si>
+    <t>화염 (Fire)</t>
+  </si>
+  <si>
+    <t>5초간 최대 체력 비례 화상 도트 데미지</t>
+  </si>
+  <si>
+    <t>서리 (Frost)</t>
+  </si>
+  <si>
+    <t>적의 이동 및 공격 모션 속도 15% 둔화</t>
+  </si>
+  <si>
+    <t>부패 (Decay)</t>
+  </si>
+  <si>
+    <t>적 방어력 감소, 이후 받는 피해량 15% 증가</t>
+  </si>
+  <si>
+    <t>이승을 떠나지 못한 망자들의 미련이 뭉친 조각.</t>
+  </si>
+  <si>
+    <t>Unlock_Condition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Currency</t>
-  </si>
-  <si>
-    <t>R_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Raw</t>
-  </si>
-  <si>
-    <t>R_002</t>
-  </si>
-  <si>
-    <t>R_003</t>
-  </si>
-  <si>
-    <t>P_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Processed</t>
-  </si>
-  <si>
-    <t>P_002</t>
-  </si>
-  <si>
-    <t>P_003</t>
-  </si>
-  <si>
-    <t>S_000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>BossSoul</t>
-  </si>
-  <si>
-    <t>S_001</t>
-  </si>
-  <si>
-    <t>S_002</t>
-  </si>
-  <si>
-    <t>S_003</t>
-  </si>
-  <si>
-    <t>Max_Stack</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>망자의 유물</t>
-  </si>
-  <si>
-    <t>오염된 야수의 뼈</t>
-  </si>
-  <si>
-    <t>1구역 짐승들에게서 얻은 탁하고 붉은 뼛조각.</t>
-  </si>
-  <si>
-    <t>일그러진 강철 파편</t>
-  </si>
-  <si>
-    <t>2구역 언데드 기사형 몬스터 드랍 전리품.</t>
-  </si>
-  <si>
-    <t>심연의 진흙</t>
-  </si>
-  <si>
-    <t>상위 구역 몬스터 드랍 전리품.</t>
-  </si>
-  <si>
-    <t>정화된 뼛가루</t>
-  </si>
-  <si>
-    <t>항아리에서 정화한 하얀 가루. (1~3강 재료)</t>
-  </si>
-  <si>
-    <t>진혼의 쐐기석</t>
-  </si>
-  <si>
-    <t>강철과 유물을 벼려낸 결정. (4~6강 재료)</t>
-  </si>
-  <si>
-    <t>망각의 결정</t>
-  </si>
-  <si>
-    <t>최종 무기 강화 재료. (7~10강 재료)</t>
-  </si>
-  <si>
-    <t>늑대 왕의 영혼</t>
-  </si>
-  <si>
-    <t>튜토리얼 0F 보스 처치 보상 (대지 속성)</t>
-  </si>
-  <si>
-    <t>(테마 1 보스)의 영혼</t>
-  </si>
-  <si>
-    <t>테마 1 메인 보스 처치 보상 (화염 속성)</t>
-  </si>
-  <si>
-    <t>(테마 2 보스)의 영혼</t>
-  </si>
-  <si>
-    <t>테마 2 메인 보스 처치 보상 (서리 속성)</t>
-  </si>
-  <si>
-    <t>(테마 3 보스)의 영혼</t>
-  </si>
-  <si>
-    <t>테마 3 메인 보스 처치 보상 (부패 속성)</t>
-  </si>
-  <si>
-    <t>Result_Id</t>
-  </si>
-  <si>
-    <t>Result_Amt</t>
-  </si>
-  <si>
-    <t>Mat_Id</t>
-  </si>
-  <si>
-    <t>Mat_Amt</t>
-  </si>
-  <si>
-    <t>Cost_Id</t>
-  </si>
-  <si>
-    <t>Cost_Amt</t>
-  </si>
-  <si>
-    <t>Potion_Lv</t>
-  </si>
-  <si>
-    <t>Max_Count</t>
-  </si>
-  <si>
-    <t>Heal_Percent</t>
-  </si>
-  <si>
-    <t>Req_Mat_Id_1</t>
-  </si>
-  <si>
-    <t>Req_Mat_Amt_1</t>
-  </si>
-  <si>
-    <t>Req_Mat_Id_2</t>
-  </si>
-  <si>
-    <t>Req_Mat_Amt_2</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>AI_Id</t>
-  </si>
-  <si>
-    <t>Unlock_Condition</t>
-  </si>
-  <si>
-    <t>AI_001</t>
-  </si>
-  <si>
-    <t>충견의 영혼</t>
-  </si>
-  <si>
-    <t>Clear_0F (자동)</t>
-  </si>
-  <si>
-    <t>AI_002</t>
-  </si>
-  <si>
-    <t>성기사의 영혼</t>
-  </si>
-  <si>
-    <t>AI_003</t>
-  </si>
-  <si>
-    <t>광전사의 영혼</t>
-  </si>
-  <si>
-    <t>Clear_1F</t>
-  </si>
-  <si>
-    <t>AI_004</t>
-  </si>
-  <si>
-    <t>궁수의 영혼</t>
-  </si>
-  <si>
-    <t>Clear_2F</t>
-  </si>
-  <si>
-    <t>Enhance_Lv</t>
-  </si>
-  <si>
-    <t>Success_Rate</t>
-  </si>
-  <si>
-    <t>Fail_Bonus</t>
-  </si>
-  <si>
-    <t>Req_Mat_Id</t>
-  </si>
-  <si>
-    <t>Req_Mat_Amt</t>
-  </si>
-  <si>
-    <t>Req_Cost_Id</t>
-  </si>
-  <si>
-    <t>Req_Cost_Amt</t>
-  </si>
-  <si>
-    <t>Soul_Id</t>
-  </si>
-  <si>
-    <t>Target_Weapon</t>
-  </si>
-  <si>
-    <t>Effect_Value</t>
-  </si>
-  <si>
-    <t>Effect_Desc</t>
-  </si>
-  <si>
-    <t>대지 (Earth)</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>강인도(Poise) 깎는 수치 20% 증가</t>
-  </si>
-  <si>
-    <t>화염 (Fire)</t>
-  </si>
-  <si>
-    <t>5초간 최대 체력 비례 화상 도트 데미지</t>
-  </si>
-  <si>
-    <t>서리 (Frost)</t>
-  </si>
-  <si>
-    <t>적의 이동 및 공격 모션 속도 15% 둔화</t>
-  </si>
-  <si>
-    <t>부패 (Decay)</t>
-  </si>
-  <si>
-    <t>적 방어력 감소, 이후 받는 피해량 15% 증가</t>
-  </si>
-  <si>
-    <t>이승을 떠나지 못한 망자들의 미련이 뭉친 조각.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -707,7 +718,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -750,6 +761,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -770,18 +784,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1213,103 +1215,103 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+        <v>151</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D2" s="8">
         <v>1.2</v>
       </c>
-      <c r="E2" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+      <c r="E2" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D3" s="8">
         <v>5</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
+      <c r="E3" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D4" s="8">
         <v>0.85</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
+      <c r="E4" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
     </row>
     <row r="5" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D5" s="8">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
+      <c r="E5" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1860,142 +1862,142 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22">
+      <c r="A2" s="3">
         <v>1001</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="4">
         <v>500</v>
       </c>
-      <c r="F2" s="23">
+      <c r="F2" s="4">
         <v>10</v>
       </c>
-      <c r="G2" s="23">
+      <c r="G2" s="4">
         <v>100</v>
       </c>
-      <c r="H2" s="23">
+      <c r="H2" s="4">
         <v>0.6</v>
       </c>
-      <c r="I2" s="23">
+      <c r="I2" s="4">
         <v>0</v>
       </c>
-      <c r="J2" s="23">
+      <c r="J2" s="4">
         <v>0</v>
       </c>
-      <c r="K2" s="23">
+      <c r="K2" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22">
+      <c r="A3" s="3">
         <v>1002</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="4">
         <v>40</v>
       </c>
-      <c r="F3" s="23">
+      <c r="F3" s="4">
         <v>5</v>
       </c>
-      <c r="G3" s="23">
+      <c r="G3" s="4">
         <v>20</v>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="4">
         <v>0</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="4">
         <v>0</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="4">
         <v>0</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22">
+      <c r="A4" s="3">
         <v>1003</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="4">
         <v>800</v>
       </c>
-      <c r="F4" s="23">
+      <c r="F4" s="4">
         <v>20</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="4">
         <v>200</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="4">
         <v>0</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="4">
         <v>0</v>
       </c>
-      <c r="J4" s="23">
+      <c r="J4" s="4">
         <v>0</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="4">
         <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22">
+      <c r="A5" s="3">
         <v>1004</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="4">
         <v>2500</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="4">
         <v>25</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="4">
         <v>500</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="4">
         <v>0.6</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="4">
         <v>300</v>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="4">
         <v>200</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="4">
         <v>500</v>
       </c>
     </row>
@@ -2022,36 +2024,36 @@
         <v>78</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="20"/>
+        <v>93</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D2" s="4">
         <v>9999</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>165</v>
+      <c r="E2" s="14" t="s">
+        <v>162</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -2059,19 +2061,19 @@
     </row>
     <row r="3" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D3" s="4">
         <v>999</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>99</v>
+      <c r="E3" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -2079,19 +2081,19 @@
     </row>
     <row r="4" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D4" s="4">
         <v>999</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>101</v>
+      <c r="E4" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -2099,19 +2101,19 @@
     </row>
     <row r="5" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4">
         <v>999</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>103</v>
+      <c r="E5" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -2119,19 +2121,19 @@
     </row>
     <row r="6" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D6" s="4">
         <v>999</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>105</v>
+      <c r="E6" s="14" t="s">
+        <v>103</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -2139,19 +2141,19 @@
     </row>
     <row r="7" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D7" s="4">
         <v>999</v>
       </c>
-      <c r="E7" s="21" t="s">
-        <v>107</v>
+      <c r="E7" s="14" t="s">
+        <v>105</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -2159,19 +2161,19 @@
     </row>
     <row r="8" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D8" s="4">
         <v>999</v>
       </c>
-      <c r="E8" s="21" t="s">
-        <v>109</v>
+      <c r="E8" s="14" t="s">
+        <v>107</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -2179,19 +2181,19 @@
     </row>
     <row r="9" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>91</v>
+        <v>167</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>111</v>
+      <c r="E9" s="14" t="s">
+        <v>109</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -2199,19 +2201,19 @@
     </row>
     <row r="10" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="21" t="s">
-        <v>113</v>
+      <c r="E10" s="14" t="s">
+        <v>111</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -2219,19 +2221,19 @@
     </row>
     <row r="11" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="21" t="s">
-        <v>115</v>
+      <c r="E11" s="14" t="s">
+        <v>113</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -2239,19 +2241,19 @@
     </row>
     <row r="12" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="21" t="s">
-        <v>117</v>
+      <c r="E12" s="14" t="s">
+        <v>115</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -2289,39 +2291,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D2" s="4">
         <v>5</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F2" s="4">
         <v>50</v>
@@ -2329,19 +2331,19 @@
     </row>
     <row r="3" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D3" s="4">
         <v>5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F3" s="4">
         <v>100</v>
@@ -2349,19 +2351,19 @@
     </row>
     <row r="4" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D4" s="4">
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F4" s="4">
         <v>300</v>
@@ -2389,25 +2391,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="12" t="s">
         <v>128</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -2421,13 +2423,13 @@
         <v>30</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E2" s="7">
         <v>0</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G2" s="8">
         <v>0</v>
@@ -2444,13 +2446,13 @@
         <v>35</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" s="7">
         <v>500</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G3" s="8">
         <v>2</v>
@@ -2467,13 +2469,13 @@
         <v>40</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" s="7">
         <v>1500</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G4" s="8">
         <v>2</v>
@@ -2506,117 +2508,117 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>130</v>
-      </c>
       <c r="G1" s="12" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D2" s="4">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D3" s="4">
         <v>2000</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F3" s="4">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" s="4">
         <v>1000</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F4" s="4">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" s="4">
         <v>3500</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2640,25 +2642,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>148</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2672,13 +2674,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G2" s="4">
         <v>100</v>
@@ -2695,13 +2697,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E3" s="4">
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G3" s="4">
         <v>150</v>
@@ -2718,13 +2720,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E4" s="4">
         <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G4" s="4">
         <v>200</v>
@@ -2741,13 +2743,13 @@
         <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E5" s="4">
         <v>5</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G5" s="4">
         <v>300</v>
@@ -2764,13 +2766,13 @@
         <v>20</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E6" s="4">
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G6" s="4">
         <v>500</v>
@@ -2787,13 +2789,13 @@
         <v>10</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E7" s="4">
         <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G7" s="4">
         <v>800</v>
@@ -2810,13 +2812,13 @@
         <v>5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E8" s="4">
         <v>5</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G8" s="4">
         <v>1200</v>
@@ -2833,13 +2835,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E9" s="4">
         <v>1</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G9" s="4">
         <v>1500</v>
@@ -2856,13 +2858,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E10" s="4">
         <v>3</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G10" s="4">
         <v>2000</v>
@@ -2879,13 +2881,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E11" s="4">
         <v>5</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G11" s="4">
         <v>3000</v>
